--- a/Outputs/Scenarios/PtX_demand_FR_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FR_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.006379959808676661</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0126410004296288</v>
+        <v>0.007716057101498001</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004213666809876268</v>
+        <v>0.009346593863518333</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>9.192442138230554e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004213666809876268</v>
+        <v>0.004005683084365001</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.009444753759612115</v>
       </c>
       <c r="K30" t="n">
-        <v>0.06765027994724196</v>
+        <v>0.04129367971396962</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02255009331574732</v>
+        <v>0.05001975080533688</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0004970923031374797</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02255009331574732</v>
+        <v>0.02143703605943009</v>
       </c>
     </row>
     <row r="43">
